--- a/01_要件定義/納品物/03_WBS.xlsx
+++ b/01_要件定義/納品物/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF19AF0-1AAD-4BDC-95B8-AB87D7C692F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44A6A4D-9FD8-4171-B0E6-675697DF659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,248 +1792,248 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2597,94 +2597,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="171" t="s">
+      <c r="B1" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="174" t="s">
+      <c r="C1" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="175"/>
-      <c r="E1" s="180" t="s">
+      <c r="D1" s="165"/>
+      <c r="E1" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="183" t="s">
+      <c r="F1" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="165">
+      <c r="G1" s="133">
         <v>45536</v>
       </c>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
-      <c r="N1" s="166"/>
-      <c r="O1" s="166"/>
-      <c r="P1" s="166"/>
-      <c r="Q1" s="166"/>
-      <c r="R1" s="166"/>
-      <c r="S1" s="166"/>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="166"/>
-      <c r="AA1" s="166"/>
-      <c r="AB1" s="166"/>
-      <c r="AC1" s="166"/>
-      <c r="AD1" s="166"/>
-      <c r="AE1" s="166"/>
-      <c r="AF1" s="166"/>
-      <c r="AG1" s="166"/>
-      <c r="AH1" s="166"/>
-      <c r="AI1" s="166"/>
-      <c r="AJ1" s="167"/>
-      <c r="AK1" s="165">
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="134"/>
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="133">
         <v>45566</v>
       </c>
-      <c r="AL1" s="166"/>
-      <c r="AM1" s="166"/>
-      <c r="AN1" s="166"/>
-      <c r="AO1" s="166"/>
-      <c r="AP1" s="166"/>
-      <c r="AQ1" s="166"/>
-      <c r="AR1" s="166"/>
-      <c r="AS1" s="166"/>
-      <c r="AT1" s="166"/>
-      <c r="AU1" s="166"/>
-      <c r="AV1" s="166"/>
-      <c r="AW1" s="166"/>
-      <c r="AX1" s="166"/>
-      <c r="AY1" s="166"/>
-      <c r="AZ1" s="166"/>
-      <c r="BA1" s="166"/>
-      <c r="BB1" s="166"/>
-      <c r="BC1" s="166"/>
-      <c r="BD1" s="166"/>
-      <c r="BE1" s="166"/>
-      <c r="BF1" s="166"/>
-      <c r="BG1" s="166"/>
-      <c r="BH1" s="166"/>
-      <c r="BI1" s="166"/>
-      <c r="BJ1" s="166"/>
-      <c r="BK1" s="166"/>
-      <c r="BL1" s="166"/>
-      <c r="BM1" s="166"/>
-      <c r="BN1" s="167"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="134"/>
+      <c r="AN1" s="134"/>
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="134"/>
+      <c r="AS1" s="134"/>
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="134"/>
+      <c r="AX1" s="134"/>
+      <c r="AY1" s="134"/>
+      <c r="AZ1" s="134"/>
+      <c r="BA1" s="134"/>
+      <c r="BB1" s="134"/>
+      <c r="BC1" s="134"/>
+      <c r="BD1" s="134"/>
+      <c r="BE1" s="134"/>
+      <c r="BF1" s="134"/>
+      <c r="BG1" s="134"/>
+      <c r="BH1" s="134"/>
+      <c r="BI1" s="134"/>
+      <c r="BJ1" s="134"/>
+      <c r="BK1" s="134"/>
+      <c r="BL1" s="134"/>
+      <c r="BM1" s="134"/>
+      <c r="BN1" s="135"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="169"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="184"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="174"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2926,12 +2926,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="170"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="185"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="175"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3114,20 +3114,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="191">
+      <c r="A4" s="145">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="194" t="s">
+      <c r="D4" s="147"/>
+      <c r="E4" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="196" t="s">
+      <c r="F4" s="150" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="89"/>
@@ -3192,12 +3192,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="187"/>
+      <c r="A5" s="137"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="141"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="151"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3260,18 +3260,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="186">
+      <c r="A6" s="136">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="152" t="s">
+      <c r="C6" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="147"/>
-      <c r="E6" s="188" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="190" t="s">
+      <c r="F6" s="143" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="47"/>
@@ -3336,12 +3336,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="187"/>
+      <c r="A7" s="137"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="144"/>
       <c r="G7" s="48"/>
       <c r="H7" s="101"/>
       <c r="I7" s="58"/>
@@ -3404,20 +3404,20 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="122">
+      <c r="A8" s="123">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="198" t="s">
+      <c r="C8" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="199"/>
-      <c r="E8" s="164" t="s">
+      <c r="D8" s="153"/>
+      <c r="E8" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="144" t="s">
+      <c r="F8" s="176" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="35"/>
@@ -3482,12 +3482,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="123"/>
+      <c r="A9" s="124"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="156"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="177"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3550,20 +3550,20 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="122">
+      <c r="A10" s="123">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="160" t="s">
+      <c r="C10" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="161"/>
-      <c r="E10" s="164" t="s">
+      <c r="D10" s="179"/>
+      <c r="E10" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="144" t="s">
+      <c r="F10" s="176" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="46"/>
@@ -3628,12 +3628,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="123"/>
+      <c r="A11" s="124"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="162"/>
-      <c r="D11" s="163"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="145"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="128"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3696,18 +3696,18 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="122">
+      <c r="A12" s="123">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="152" t="s">
+      <c r="C12" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="147"/>
-      <c r="E12" s="150" t="s">
+      <c r="D12" s="130"/>
+      <c r="E12" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="149" t="s">
+      <c r="F12" s="127" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="47"/>
@@ -3772,12 +3772,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="123"/>
+      <c r="A13" s="124"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="156"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="177"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3840,20 +3840,20 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="122">
+      <c r="A14" s="123">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="184" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="142" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="144" t="s">
+      <c r="F14" s="176" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="35"/>
@@ -3918,12 +3918,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="123"/>
+      <c r="A15" s="124"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="145"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="128"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -3986,18 +3986,18 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="122">
+      <c r="A16" s="123">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="152" t="s">
+      <c r="C16" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="147"/>
-      <c r="E16" s="148" t="s">
+      <c r="D16" s="130"/>
+      <c r="E16" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="149" t="s">
+      <c r="F16" s="127" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="47"/>
@@ -4062,12 +4062,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="123"/>
+      <c r="A17" s="124"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="145"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="128"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4130,18 +4130,18 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="122">
+      <c r="A18" s="123">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="152" t="s">
+      <c r="C18" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="147"/>
-      <c r="E18" s="148" t="s">
+      <c r="D18" s="130"/>
+      <c r="E18" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="149" t="s">
+      <c r="F18" s="127" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="48"/>
@@ -4206,12 +4206,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="123"/>
+      <c r="A19" s="124"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="156"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="189"/>
+      <c r="F19" s="177"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4274,20 +4274,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="122">
+      <c r="A20" s="123">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="127"/>
-      <c r="E20" s="142" t="s">
+      <c r="D20" s="185"/>
+      <c r="E20" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="144"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4350,14 +4350,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="123"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="145"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="128"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4420,18 +4420,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="122">
+      <c r="A22" s="123">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="146" t="s">
+      <c r="C22" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148" t="s">
+      <c r="D22" s="130"/>
+      <c r="E22" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="149"/>
+      <c r="F22" s="127"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4494,12 +4494,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="123"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="145"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="187"/>
+      <c r="F23" s="128"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4562,18 +4562,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="122">
+      <c r="A24" s="123">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="146" t="s">
+      <c r="C24" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="147"/>
-      <c r="E24" s="150" t="s">
+      <c r="D24" s="130"/>
+      <c r="E24" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="149"/>
+      <c r="F24" s="127"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4636,12 +4636,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="123"/>
+      <c r="A25" s="124"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="145"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="128"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4704,18 +4704,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="122">
+      <c r="A26" s="123">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="146" t="s">
+      <c r="C26" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="150" t="s">
+      <c r="D26" s="130"/>
+      <c r="E26" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="149"/>
+      <c r="F26" s="127"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4778,12 +4778,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="123"/>
+      <c r="A27" s="124"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="145"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="128"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4846,20 +4846,20 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="122">
+      <c r="A28" s="123">
         <v>13</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="134" t="s">
+      <c r="C28" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="130" t="s">
+      <c r="D28" s="191"/>
+      <c r="E28" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="132"/>
+      <c r="F28" s="196"/>
       <c r="G28" s="35"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4922,12 +4922,12 @@
       <c r="BN28" s="98"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="123"/>
+      <c r="A29" s="124"/>
       <c r="B29" s="31"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="139"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="195"/>
+      <c r="F29" s="144"/>
       <c r="G29" s="47"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4984,26 +4984,26 @@
       <c r="BH29" s="121"/>
       <c r="BI29" s="13"/>
       <c r="BJ29" s="19"/>
-      <c r="BK29" s="92"/>
+      <c r="BK29" s="121"/>
       <c r="BL29" s="92"/>
       <c r="BM29" s="92"/>
       <c r="BN29" s="94"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="122">
+      <c r="A30" s="123">
         <v>14</v>
       </c>
-      <c r="B30" s="124" t="s">
+      <c r="B30" s="197" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C30" s="184" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="130" t="s">
+      <c r="D30" s="185"/>
+      <c r="E30" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="132"/>
+      <c r="F30" s="196"/>
       <c r="G30" s="35"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -5066,12 +5066,12 @@
       <c r="BN30" s="98"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A31" s="123"/>
-      <c r="B31" s="125"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="133"/>
+      <c r="A31" s="124"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="199"/>
+      <c r="D31" s="200"/>
+      <c r="E31" s="201"/>
+      <c r="F31" s="202"/>
       <c r="G31" s="36"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5125,10 +5125,10 @@
       <c r="BE31" s="63"/>
       <c r="BF31" s="63"/>
       <c r="BG31" s="63"/>
-      <c r="BH31" s="202"/>
+      <c r="BH31" s="122"/>
       <c r="BI31" s="14"/>
       <c r="BJ31" s="20"/>
-      <c r="BK31" s="99"/>
+      <c r="BK31" s="122"/>
       <c r="BL31" s="99"/>
       <c r="BM31" s="99"/>
       <c r="BN31" s="100"/>
@@ -5157,6 +5157,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
@@ -5173,54 +5221,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
